--- a/delivery_date.xlsx
+++ b/delivery_date.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\study python\python_work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F56C0D-DD5D-4070-B14E-54FF1014DC11}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4942F9B1-DBBC-40AF-8886-587AF25A7F30}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>ID</t>
   </si>
@@ -34,9 +34,6 @@
   </si>
   <si>
     <t>Ready to move</t>
-  </si>
-  <si>
-    <t>Unknown</t>
   </si>
   <si>
     <t>soon</t>
@@ -415,8 +412,8 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>3</v>
+      <c r="B4">
+        <v>2021</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
@@ -432,7 +429,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
@@ -448,7 +445,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
